--- a/CheckNMate_DB_final.xlsx
+++ b/CheckNMate_DB_final.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hemabalaji/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F5328D-27B1-0045-B8C8-78C457244891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16420" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Students" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Attendance" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Class Logs" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Franchises" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Users" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="Audit_Logs" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="Company_Profile" sheetId="7" r:id="rId11"/>
+    <sheet name="Students" sheetId="1" r:id="rId1"/>
+    <sheet name="Attendance" sheetId="2" r:id="rId2"/>
+    <sheet name="Class Logs" sheetId="3" r:id="rId3"/>
+    <sheet name="Franchises" sheetId="4" r:id="rId4"/>
+    <sheet name="Users" sheetId="5" r:id="rId5"/>
+    <sheet name="Audit_Logs" sheetId="6" r:id="rId6"/>
+    <sheet name="Company_Profile" sheetId="7" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -163,9 +172,6 @@
     <t>Check N Mate</t>
   </si>
   <si>
-    <t>placeholder_hash_john</t>
-  </si>
-  <si>
     <t>Support_Phone</t>
   </si>
   <si>
@@ -197,36 +203,45 @@
   </si>
   <si>
     <t>monthly_fee_reminder_v1</t>
+  </si>
+  <si>
+    <t>$2b$12$AM0GBXKgz2ZOvIcWMZheOuzNGm2/R3QyTjSq4/sSS2KdxIOOkPjtq</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -234,77 +249,51 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -494,21 +483,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="15.5"/>
-    <col customWidth="1" min="5" max="5" width="20.13"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -525,7 +517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -542,7 +534,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -560,41 +552,42 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="13.63"/>
-    <col customWidth="1" min="3" max="3" width="13.38"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3">
-        <v>46235.0</v>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2">
+        <v>46235</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
@@ -609,9 +602,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3">
-        <v>46235.0</v>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="2">
+        <v>46235</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>15</v>
@@ -627,40 +620,41 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="14.13"/>
-    <col customWidth="1" min="3" max="3" width="13.38"/>
-    <col customWidth="1" min="4" max="4" width="29.5"/>
+    <col min="2" max="2" width="14.1640625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="29.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2">
-      <c r="A2" s="3">
-        <v>46235.0</v>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2">
+        <v>46235</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
@@ -671,9 +665,9 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3">
-      <c r="A3" s="3">
-        <v>46235.0</v>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="2">
+        <v>46235</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>15</v>
@@ -685,34 +679,35 @@
       <c r="E3" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="15.25"/>
-    <col customWidth="1" min="3" max="3" width="13.63"/>
-    <col customWidth="1" min="4" max="4" width="14.63"/>
+    <col min="2" max="2" width="15.1640625" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -723,7 +718,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -735,43 +730,44 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="9.75"/>
-    <col customWidth="1" min="2" max="2" width="12.25"/>
-    <col customWidth="1" min="3" max="3" width="19.63"/>
-    <col customWidth="1" min="4" max="4" width="8.0"/>
-    <col customWidth="1" min="5" max="5" width="18.75"/>
+    <col min="1" max="1" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -787,7 +783,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -795,61 +791,62 @@
         <v>46</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="B4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="4">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3">
         <v>46241.416666666664</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -863,14 +860,14 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -878,25 +875,26 @@
       <c r="E4" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.75"/>
-    <col customWidth="1" min="2" max="2" width="27.13"/>
-    <col customWidth="1" min="3" max="3" width="12.63"/>
-    <col customWidth="1" min="5" max="5" width="19.63"/>
-    <col customWidth="1" min="6" max="6" width="21.75"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
@@ -905,7 +903,7 @@
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>45</v>
       </c>
@@ -914,46 +912,46 @@
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>56</v>
+      <c r="B5" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="C6" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="B5"/>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/CheckNMate_DB_final.xlsx
+++ b/CheckNMate_DB_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hemabalaji/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F5328D-27B1-0045-B8C8-78C457244891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8492CFC-88FD-0A41-BC2B-BB3799DD3E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16420" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,7 +205,7 @@
     <t>monthly_fee_reminder_v1</t>
   </si>
   <si>
-    <t>$2b$12$AM0GBXKgz2ZOvIcWMZheOuzNGm2/R3QyTjSq4/sSS2KdxIOOkPjtq</t>
+    <t>$2b$12$FkS.eL5MD4HQydqNlFftEuMgFlHATpKhffXAq1pFYntyGS3MuQ8xm</t>
   </si>
 </sst>
 </file>
